--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Pramod Ojha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851152370</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851152370</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9851152370</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9851152370</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -948,25 +942,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L32-5</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1015,7 +1005,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1306,7 +1296,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,18 +483,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -523,18 +523,18 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -980,6 +980,527 @@
         </is>
       </c>
       <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:58 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356940</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Abhishek Kc</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Abhishek Kc</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9861021835</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:58:58 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9861021835</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:55:03 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:58:58 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.74539</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>near Nirvana Home. Hotel &amp; Suites pipal marg kathmandu -03 maharajgunj, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>abhishekkc348@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>02:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L16-2</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.33838</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>17h 3m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:53 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr"/>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:49 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355352</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9849025416</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:49:17 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9849025416</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:03:59 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:49:17 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.75259</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Yoga Home Tarkeshwor-5, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>parkasnepal423@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L62-4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.2867</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 45m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -996,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1005,7 +1526,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1033,7 +1554,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1043,7 +1564,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1054,7 +1575,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1599,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 13m</t>
+          <t>1d 7h 8m</t>
         </is>
       </c>
     </row>
@@ -1119,214 +1640,310 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="C15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1355218</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Pramod Ojha</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>02 Oct 2026 01:14:05 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>1d 21h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356940</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Abhishek Kc</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:58:58 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:55:03 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:58:58 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>17h 3m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -1052,10 +1052,8 @@
           <t>Abhishek Kc</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9861021835</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9861021835</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1070,10 +1068,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9861021835</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9861021835</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1090,10 +1086,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.74539</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.74539</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1149,25 +1143,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L16-2</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.33838</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.33838</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1366,10 +1356,8 @@
           <t>Parkas Nepal</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9849025416</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9849025416</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1384,10 +1372,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9849025416</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9849025416</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1404,10 +1390,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.75259</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.75259</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1459,48 +1443,768 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L62-4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.2867</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.2867</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 45m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS5" s="3" t="inlineStr">
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:59 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:17 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356816</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Regmi</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Regmi</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9841932852</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:17:09 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9841932852</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 04:39:49 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:17:09 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.75124</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Grande Villa,Tokha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>rgmibishal55@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L3-1</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.32164</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 45m</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV5" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>18h 37m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:12 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356816</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Regmi</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Regmi</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9841932852</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:17:09 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9841932852</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 04:39:49 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:17:09 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.75124</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near Grande Villa,Tokha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>rgmibishal55@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L3-1</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.32164</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>18h 37m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:09 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356816</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Regmi</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Regmi</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841932852</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:17:09 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841932852</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 04:39:49 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:17:09 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.75124</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Near Grande Villa,Tokha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>rgmibishal55@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L3-1</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.32164</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>18h 37m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1526,7 +2230,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1554,7 +2258,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1575,7 +2279,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1640,14 +2344,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1712,14 +2416,14 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1913,7 +2617,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1656,10 +1656,8 @@
           <t>Bishal Regmi</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9841932852</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9841932852</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1674,10 +1672,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9841932852</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9841932852</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1694,10 +1690,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.75124</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.75124</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1749,25 +1743,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L3-1</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.32164</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.32164</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -1863,10 +1853,8 @@
           <t>Bishal Regmi</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9841932852</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9841932852</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -1881,10 +1869,8 @@
       </c>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>9841932852</t>
-        </is>
+      <c r="U8" s="3" t="n">
+        <v>9841932852</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1901,10 +1887,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.75124</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.75124</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -1956,25 +1940,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L3-1</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.32164</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.32164</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2070,10 +2050,8 @@
           <t>Bishal Regmi</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841932852</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841932852</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2088,10 +2066,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>9841932852</t>
-        </is>
+      <c r="U9" s="3" t="n">
+        <v>9841932852</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -2108,10 +2084,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.75124</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.75124</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2163,25 +2137,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L3-1</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.32164</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.32164</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,40 +496,40 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="27" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="18" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2180,6 +2180,627 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:18 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357161</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Pradip chandra Poudel</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Pradip chandra Poudel</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841344588</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:18:45 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841344588</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:36:19 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:18:45 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.743029</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Tarkeshwor  sesmati 11 nepaltar kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>shobhaadkh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L25-5</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.30149</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>13h 42m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:44 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355047</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Unish Dulal</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Unish Dulal</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9803282720</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:44:04 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9803282720</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:58:05 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:44:04 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>BhaktapurKaushaltaarTersetaar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>dunish550@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>18:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 45m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:40 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356549</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Ghimire</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Ghimire</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841728801</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841728801</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:40:08 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>near by Peace Homestay - Homestay P7HV+QHM Janajagriti Marg Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>9841728801@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB352</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>21h 56m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>21h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2191,16 +2812,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2228,7 +2849,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2238,7 +2859,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2249,7 +2870,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2894,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 7h 8m</t>
+          <t>1d 6h 56m</t>
         </is>
       </c>
     </row>
@@ -2314,14 +2935,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -2386,238 +3007,395 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
       <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1355218</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Pramod Ojha</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 01:14:05 PM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 13m</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>TKT1355218</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Pramod Ojha</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:27:28 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 01:14:05 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:27:28 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>1d 21h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>TKT1356940</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Abhishek Kc</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 05:55:03 PM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>17h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357161</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Pradip chandra Poudel</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:18:45 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:36:19 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:18:45 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>13h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355047</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Unish Dulal</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:44:04 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:58:05 AM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:44:04 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 45m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2247,10 +2247,8 @@
           <t>Pradip chandra Poudel</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841344588</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841344588</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2285,10 +2283,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.743029</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.743029</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2344,25 +2340,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L25-5</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.30149</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.30149</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2458,10 +2450,8 @@
           <t>Unish Dulal</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9803282720</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9803282720</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2496,10 +2486,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2555,25 +2543,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2669,10 +2653,8 @@
           <t>Ambika Ghimire</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841728801</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841728801</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2758,10 +2740,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
@@ -2772,32 +2752,540 @@
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>21h 56m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>21h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>21h 56m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>21h 56m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:56 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356346</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Suresh maharjan</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Suresh maharjan</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9841213338</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:57:03 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9841213338</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:20:49 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:57:03 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Lampati marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>08:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB303</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 36m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -2812,12 +3300,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -2849,7 +3337,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2859,7 +3347,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2870,7 +3358,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +3382,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 6h 56m</t>
+          <t>1d 5h 40m</t>
         </is>
       </c>
     </row>
@@ -2947,74 +3435,69 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>37.5%</t>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -3026,254 +3509,166 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355218</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Pramod Ojha</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 01:14:05 PM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>1d 21h 13m</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1356940</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Abhishek Kc</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 05:55:03 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>17h 3m</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1357161</t>
+          <t>TKT1355218</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Pradip chandra Poudel</t>
+          <t>Pramod Ojha</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3298,27 +3693,27 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 09:36:19 PM</t>
+          <t>02 Oct 2026 01:14:05 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -3328,74 +3723,275 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>13h 42m</t>
+          <t>1d 21h 13m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>TKT1356940</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Abhishek Kc</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:58:58 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:55:03 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:58:58 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>17h 3m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357161</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Pradip chandra Poudel</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:18:45 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:36:19 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:18:45 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>13h 42m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>TKT1355047</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Unish Dulal</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade Dual Band</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>02 Oct 2026 11:58:05 AM</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>1d 23h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356346</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Suresh maharjan</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:57:03 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:20:49 AM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:57:03 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>1d 36m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW16"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3157,10 +3157,8 @@
           <t>Suresh maharjan</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9841213338</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9841213338</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3246,10 +3244,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -3260,32 +3256,239 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 36m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS16" s="3" t="inlineStr">
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:03 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356614</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Surendra Aryal</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Surendra Aryal</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9867646414</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:03:09 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9867646414</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:18:47 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:03:09 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.736057</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>????? ????? ?????? ????? - School P8P7+VFR Kathmandu 44600  user id ; 9867646414, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>05:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L46-3</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.313743</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>1d 36m</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV16" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW16" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3337,7 +3540,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3347,7 +3550,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3358,7 +3561,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3585,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 5h 40m</t>
+          <t>1d 4h 21m</t>
         </is>
       </c>
     </row>
@@ -3423,14 +3626,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3513,14 +3716,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -3961,14 +4164,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 11:57:03 AM</t>
@@ -3992,6 +4195,73 @@
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>1d 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356614</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Surendra Aryal</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:03:09 PM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:18:47 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:03:09 PM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3352,10 +3352,8 @@
           <t>Surendra Aryal</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9867646414</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9867646414</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3390,10 +3388,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.736057</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.736057</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3445,48 +3441,255 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>L46-3</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.313743</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.313743</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:23 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357724</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Tara Natha Yogi</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Tara Natha Yogi</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9868922722</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:23:38 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9868922722</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:39:55 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:23:38 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.744355</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Near Ishan Children &amp; Women's Hospital Pvt. Ltd. - Hospital Kalkinarayan Tole Kathmandu 44600, Bagm</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>tyogi204@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L1-7</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.332816</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>21h 44m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>43m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW17" s="3" t="inlineStr">
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3503,7 +3706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3540,7 +3743,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -3550,7 +3753,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -3561,7 +3764,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3788,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 4h 21m</t>
+          <t>1d 24m</t>
         </is>
       </c>
     </row>
@@ -3626,14 +3829,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -3716,14 +3919,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4231,14 +4434,14 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:03:09 PM</t>
@@ -4262,6 +4465,73 @@
       <c r="M28" s="3" t="inlineStr">
         <is>
           <t>21h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357724</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Tara Natha Yogi</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:23:38 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:39:55 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:23:38 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>43m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW18"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -512,13 +512,13 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -3551,10 +3551,8 @@
           <t>Tara Natha Yogi</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9868922722</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9868922722</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -3589,10 +3587,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.744355</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.744355</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -3648,50 +3644,870 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L1-7</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.332816</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.33281599999999</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>43m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:45 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355876</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Khatri</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Khatri</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9702617283</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:45:35 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>BKT9702617283</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 07:38:32 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:45:35 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Suryabinayak Chowk near Ganesh mandir , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>9861283872@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>10:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L24-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>43m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 7m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356999</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Kapil Basnet</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Kapil Basnet</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9843187926</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:13 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9843187926</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 06:44:04 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:13 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Gundu Rato pati, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr"/>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>01:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L1-CDB8</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>17h 53m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357672</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9851045120</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43:41 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851045120</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:12:11 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43:41 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Sunflower Academy (English Medium SS) - Educational institution Q822+54F way Tarakeshwar 44600, Bagm</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>9851045120@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1h 31m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:40 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wiif 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357801</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Dammar Bahadur Gurung</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Dammar Bahadur Gurung</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9841649762</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:15:52 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9841649762</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:15:52 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:40:37 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.72156</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Near Prime College, Nayabazar, Pahikwo Sadak, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>dammarshlnepal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.30356</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>24m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>24m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -3706,13 +4522,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -3743,7 +4559,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -3753,7 +4569,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3764,7 +4580,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -3776,7 +4592,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>2m</t>
         </is>
       </c>
     </row>
@@ -3788,7 +4604,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 24m</t>
+          <t>21h 4m</t>
         </is>
       </c>
     </row>
@@ -3829,14 +4645,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -3847,10 +4663,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -3919,14 +4735,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -3961,7 +4777,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -3977,171 +4793,127 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355218</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Pramod Ojha</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 01:14:05 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>1d 21h 13m</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1356940</t>
+          <t>TKT1355218</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Abhishek Kc</t>
+          <t>Pramod Ojha</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4171,22 +4943,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 05:55:03 PM</t>
+          <t>02 Oct 2026 01:14:05 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -4196,19 +4968,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>17h 3m</t>
+          <t>1d 21h 13m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1357161</t>
+          <t>TKT1356940</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Pradip chandra Poudel</t>
+          <t>Abhishek Kc</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4238,22 +5010,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 09:36:19 PM</t>
+          <t>03 Oct 2026 05:55:03 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4263,19 +5035,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>13h 42m</t>
+          <t>17h 3m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1355047</t>
+          <t>TKT1357161</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Unish Dulal</t>
+          <t>Pradip chandra Poudel</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4285,7 +5057,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -4305,22 +5077,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:44:04 AM</t>
+          <t>04 Oct 2026 11:18:45 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 11:58:05 AM</t>
+          <t>03 Oct 2026 09:36:19 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:44:04 AM</t>
+          <t>04 Oct 2026 11:18:45 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4330,29 +5102,29 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 45m</t>
+          <t>13h 42m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1356346</t>
+          <t>TKT1355047</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Suresh maharjan</t>
+          <t>Unish Dulal</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -4372,22 +5144,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:57:03 AM</t>
+          <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:20:49 AM</t>
+          <t>02 Oct 2026 11:58:05 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:57:03 AM</t>
+          <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4397,29 +5169,29 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 36m</t>
+          <t>1d 23h 45m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1356614</t>
+          <t>TKT1356346</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Surendra Aryal</t>
+          <t>Suresh maharjan</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4439,22 +5211,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:03:09 PM</t>
+          <t>04 Oct 2026 11:57:03 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:18:47 PM</t>
+          <t>03 Oct 2026 11:20:49 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:03:09 PM</t>
+          <t>04 Oct 2026 11:57:03 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4464,74 +5236,409 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>1d 36m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>TKT1356614</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Surendra Aryal</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:03:09 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:18:47 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:03:09 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>21h 44m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1357724</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Tara Natha Yogi</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:23:38 PM</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 11:39:55 AM</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:23:38 PM</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355876</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Kamal Khatri</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:45:35 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 07:38:32 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:45:35 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>1d 17h 7m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356999</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Kapil Basnet</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:13 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 06:44:04 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:37:13 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>17h 53m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357672</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43:41 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:12:11 AM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43:41 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357801</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Dammar Bahadur Gurung</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:15:52 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:15:52 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:40:37 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>24m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>24m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW22"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -527,7 +527,7 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -3754,10 +3754,8 @@
           <t>Kamal Khatri</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9702617283</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9702617283</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -3829,10 +3827,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH19" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH19" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
@@ -3851,10 +3847,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -3865,7 +3859,7 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -3961,10 +3955,8 @@
           <t>Kapil Basnet</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9843187926</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9843187926</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4032,10 +4024,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH20" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH20" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
@@ -4054,10 +4044,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4068,7 +4056,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4164,10 +4152,8 @@
           <t>Dinesh Shrestha</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9851045120</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9851045120</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4257,10 +4243,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4271,7 +4255,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4367,10 +4351,8 @@
           <t>Dammar Bahadur Gurung</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9841649762</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9841649762</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4405,10 +4387,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.72156</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.72156</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4464,48 +4444,251 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.30356</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.30356</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>24m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>24m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
           <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>24m</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr">
-        <is>
-          <t>24m</t>
-        </is>
-      </c>
-      <c r="AU22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>STB connection</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357113</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Thapa</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Preeti Thapa</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9767483764</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:30:41 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>KLK9767483764</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:30:41 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:47:34 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.701463887608504</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>ktm manamaijuengal hot school, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>thapa76@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>L31-5</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.3304672241211</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>16h 16m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>16h 16m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : STB connection  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -4522,7 +4705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4531,7 +4714,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4559,7 +4742,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4580,7 +4763,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4645,14 +4828,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -4731,18 +4914,18 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4754,30 +4937,30 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -4800,7 +4983,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -4816,171 +4999,127 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1355218</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Pramod Ojha</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 01:14:05 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 13m</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1356940</t>
+          <t>TKT1355218</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Abhishek Kc</t>
+          <t>Pramod Ojha</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -5010,22 +5149,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 05:55:03 PM</t>
+          <t>02 Oct 2026 01:14:05 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -5035,19 +5174,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>17h 3m</t>
+          <t>1d 21h 13m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1357161</t>
+          <t>TKT1356940</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Pradip chandra Poudel</t>
+          <t>Abhishek Kc</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -5077,22 +5216,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 09:36:19 PM</t>
+          <t>03 Oct 2026 05:55:03 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -5102,19 +5241,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>13h 42m</t>
+          <t>17h 3m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1355047</t>
+          <t>TKT1357161</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Unish Dulal</t>
+          <t>Pradip chandra Poudel</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -5124,7 +5263,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -5144,22 +5283,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:44:04 AM</t>
+          <t>04 Oct 2026 11:18:45 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 11:58:05 AM</t>
+          <t>03 Oct 2026 09:36:19 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:44:04 AM</t>
+          <t>04 Oct 2026 11:18:45 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -5169,29 +5308,29 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 45m</t>
+          <t>13h 42m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1356346</t>
+          <t>TKT1355047</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Suresh maharjan</t>
+          <t>Unish Dulal</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -5211,22 +5350,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:57:03 AM</t>
+          <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:20:49 AM</t>
+          <t>02 Oct 2026 11:58:05 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:57:03 AM</t>
+          <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -5236,29 +5375,29 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 36m</t>
+          <t>1d 23h 45m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1356614</t>
+          <t>TKT1356346</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Surendra Aryal</t>
+          <t>Suresh maharjan</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -5278,22 +5417,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:03:09 PM</t>
+          <t>04 Oct 2026 11:57:03 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:18:47 PM</t>
+          <t>03 Oct 2026 11:20:49 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:03:09 PM</t>
+          <t>04 Oct 2026 11:57:03 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5303,19 +5442,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>1d 36m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1357724</t>
+          <t>TKT1356614</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Tara Natha Yogi</t>
+          <t>Surendra Aryal</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5345,22 +5484,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:23:38 PM</t>
+          <t>04 Oct 2026 12:03:09 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:39:55 AM</t>
+          <t>03 Oct 2026 02:18:47 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:23:38 PM</t>
+          <t>04 Oct 2026 12:03:09 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5370,19 +5509,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1355876</t>
+          <t>TKT1357724</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Kamal Khatri</t>
+          <t>Tara Natha Yogi</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5407,27 +5546,27 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:45:35 PM</t>
+          <t>04 Oct 2026 12:23:38 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 07:38:32 PM</t>
+          <t>04 Oct 2026 11:39:55 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:45:35 PM</t>
+          <t>04 Oct 2026 12:23:38 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5437,29 +5576,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 17h 7m</t>
+          <t>43m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1356999</t>
+          <t>TKT1355876</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Kapil Basnet</t>
+          <t>Kamal Khatri</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -5474,27 +5613,27 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:13 PM</t>
+          <t>04 Oct 2026 12:45:35 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 06:44:04 PM</t>
+          <t>02 Oct 2026 07:38:32 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:13 PM</t>
+          <t>04 Oct 2026 12:45:35 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5504,29 +5643,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>17h 53m</t>
+          <t>1d 17h 7m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1357672</t>
+          <t>TKT1356999</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Dinesh Shrestha</t>
+          <t>Kapil Basnet</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -5541,27 +5680,27 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:43:41 PM</t>
+          <t>04 Oct 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:12:11 AM</t>
+          <t>03 Oct 2026 06:44:04 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:43:41 PM</t>
+          <t>04 Oct 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -5571,72 +5710,139 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>17h 53m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>TKT1357672</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43:41 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:12:11 AM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43:41 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>TKT1357801</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Dammar Bahadur Gurung</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:15:52 PM</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:15:52 PM</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:40:37 PM</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>24m</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>24m</t>
         </is>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="21" customWidth="1" min="25" max="25"/>
+    <col width="19" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4554,10 +4554,8 @@
           <t>Preeti Thapa</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9767483764</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9767483764</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4592,10 +4590,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.701463887608504</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.7014638876085</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -4647,25 +4643,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>L31-5</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.3304672241211</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.33046722412109</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : STB connection  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4686,6 +4686,109 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 1:54 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr"/>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr"/>
+      <c r="V24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr"/>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr"/>
+      <c r="AA24" s="3" t="inlineStr"/>
+      <c r="AB24" s="3" t="inlineStr"/>
+      <c r="AC24" s="3" t="inlineStr"/>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr"/>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4734,7 +4837,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -4755,7 +4858,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW24"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4789,6 +4789,408 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 2:04 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356209</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Arjun Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Arjun Bahadur Singh</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9709913337</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:28:03 AM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>KLK9709913337</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:28:03 AM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:04:10 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Academy - Middle school P75G+2M3 Nagarjun 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>9709913337@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 36m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 36m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 2:02 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV not working</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357818</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Uma Manandhar</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Uma Manandhar</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9860913842</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:02:21 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9860913842</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:22:29 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:02:21 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr"/>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Near Tundal Devi Temple, Bishalnagar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>mndruma@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L17-1</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr"/>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1h 39m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4800,16 +5202,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4837,7 +5239,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -4847,7 +5249,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -4858,7 +5260,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -4882,7 +5284,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 4m</t>
+          <t>19h 27m</t>
         </is>
       </c>
     </row>
@@ -4923,14 +5325,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -4941,10 +5343,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -5036,14 +5438,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5480,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -5101,7 +5503,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -5117,171 +5519,127 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355218</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Pramod Ojha</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 01:14:05 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>1d 21h 13m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1356940</t>
+          <t>TKT1355218</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Abhishek Kc</t>
+          <t>Pramod Ojha</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -5311,22 +5669,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 05:55:03 PM</t>
+          <t>02 Oct 2026 01:14:05 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -5336,19 +5694,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>17h 3m</t>
+          <t>1d 21h 13m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1357161</t>
+          <t>TKT1356940</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Pradip chandra Poudel</t>
+          <t>Abhishek Kc</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -5378,22 +5736,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 09:36:19 PM</t>
+          <t>03 Oct 2026 05:55:03 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -5403,19 +5761,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>13h 42m</t>
+          <t>17h 3m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1355047</t>
+          <t>TKT1357161</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Unish Dulal</t>
+          <t>Pradip chandra Poudel</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5425,7 +5783,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -5445,22 +5803,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:44:04 AM</t>
+          <t>04 Oct 2026 11:18:45 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 11:58:05 AM</t>
+          <t>03 Oct 2026 09:36:19 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:44:04 AM</t>
+          <t>04 Oct 2026 11:18:45 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -5470,29 +5828,29 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 45m</t>
+          <t>13h 42m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1356346</t>
+          <t>TKT1355047</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Suresh maharjan</t>
+          <t>Unish Dulal</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -5512,22 +5870,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:57:03 AM</t>
+          <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:20:49 AM</t>
+          <t>02 Oct 2026 11:58:05 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:57:03 AM</t>
+          <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -5537,29 +5895,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 36m</t>
+          <t>1d 23h 45m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1356614</t>
+          <t>TKT1356346</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Surendra Aryal</t>
+          <t>Suresh maharjan</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -5579,22 +5937,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:03:09 PM</t>
+          <t>04 Oct 2026 11:57:03 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:18:47 PM</t>
+          <t>03 Oct 2026 11:20:49 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:03:09 PM</t>
+          <t>04 Oct 2026 11:57:03 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -5604,19 +5962,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>1d 36m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1357724</t>
+          <t>TKT1356614</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Tara Natha Yogi</t>
+          <t>Surendra Aryal</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -5646,22 +6004,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:23:38 PM</t>
+          <t>04 Oct 2026 12:03:09 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:39:55 AM</t>
+          <t>03 Oct 2026 02:18:47 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:23:38 PM</t>
+          <t>04 Oct 2026 12:03:09 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -5671,19 +6029,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1355876</t>
+          <t>TKT1357724</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Kamal Khatri</t>
+          <t>Tara Natha Yogi</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5713,22 +6071,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:45:35 PM</t>
+          <t>04 Oct 2026 12:23:38 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 07:38:32 PM</t>
+          <t>04 Oct 2026 11:39:55 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:45:35 PM</t>
+          <t>04 Oct 2026 12:23:38 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -5738,29 +6096,29 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 7m</t>
+          <t>43m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1356999</t>
+          <t>TKT1355876</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Kapil Basnet</t>
+          <t>Kamal Khatri</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -5780,22 +6138,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:13 PM</t>
+          <t>04 Oct 2026 12:45:35 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 06:44:04 PM</t>
+          <t>02 Oct 2026 07:38:32 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:13 PM</t>
+          <t>04 Oct 2026 12:45:35 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -5805,29 +6163,29 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>17h 53m</t>
+          <t>1d 17h 7m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1357672</t>
+          <t>TKT1356999</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Dinesh Shrestha</t>
+          <t>Kapil Basnet</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -5847,22 +6205,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:43:41 PM</t>
+          <t>04 Oct 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:12:11 AM</t>
+          <t>03 Oct 2026 06:44:04 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:43:41 PM</t>
+          <t>04 Oct 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -5872,74 +6230,208 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>17h 53m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>TKT1357672</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Dinesh Shrestha</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43:41 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:12:11 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:43:41 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>1h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>TKT1357801</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Dammar Bahadur Gurung</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:15:52 PM</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:15:52 PM</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 12:40:37 PM</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>24m</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M36" s="3" t="inlineStr">
         <is>
           <t>24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357818</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Uma Manandhar</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:02:21 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 12:22:29 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:02:21 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>1h 39m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4856,10 +4856,8 @@
           <t>Arjun Bahadur Singh</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9709913337</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9709913337</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -4945,10 +4943,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -4959,7 +4955,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5055,10 +5051,8 @@
           <t>Uma Manandhar</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9860913842</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9860913842</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5148,10 +5142,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
@@ -5162,7 +5154,7 @@
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5211,7 +5203,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6401,7 +6393,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5183,6 +5183,217 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 2:18 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355431</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Ramkhrishna Mijar</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Ramkhrishna Mijar</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9841511829</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:18:12 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9841511829</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:33:53 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:18:12 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.73537</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Maharajgung,Kathmandu,Near by metro hospital, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>royab.kapali@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>15:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L38-3</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.35739</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 44m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5194,7 +5405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5203,7 +5414,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5231,7 +5442,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -5241,7 +5452,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -5252,7 +5463,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5475,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>1m</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5487,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 27m</t>
+          <t>21h 37m</t>
         </is>
       </c>
     </row>
@@ -5317,14 +5528,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
     </row>
@@ -5430,14 +5641,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -6427,6 +6638,73 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355431</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Ramkhrishna Mijar</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:18:12 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:33:53 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 02:18:12 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 44m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5250,10 +5250,8 @@
           <t>Ramkhrishna Mijar</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9841511829</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9841511829</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5288,10 +5286,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.73537</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.73537</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -5347,25 +5343,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>L38-3</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.35739</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.35739</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5414,7 +5406,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6671,7 +6663,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5386,6 +5386,217 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 3:46 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357417</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Swisha Adventure Travel</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Swisha Adventure Travel</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9856039498</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:21:42 AM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9856039498</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:21:42 AM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:46:58 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.7157</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Near Hotel Tradition and Spa ,Saat Ghumti Marg, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>nepalswisha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.3096</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5397,7 +5608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5406,7 +5617,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5434,7 +5645,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -5444,7 +5655,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -5455,7 +5666,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5678,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>29m</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5690,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 37m</t>
+          <t>20h 32m</t>
         </is>
       </c>
     </row>
@@ -5520,14 +5731,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
     </row>
@@ -5633,14 +5844,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -6697,6 +6908,73 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357417</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Swisha Adventure Travel</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:21:42 AM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:21:42 AM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:46:58 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW28"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -5453,10 +5453,8 @@
           <t>Swisha Adventure Travel</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9856039498</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9856039498</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5491,10 +5489,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.7157</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.7157</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -5550,48 +5546,868 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.3096</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.3096</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>6h 25m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>6h 25m</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>6h 25m</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV28" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 3:49 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357696</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Romiyana Neupane</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Romiyana Neupane</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9700393777</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:17 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9700393777</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:22:10 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:17 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Bode kamal pokhari Bode kamal pokhari - Pond Madhyapur Thimi 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>romeeyana@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>4h 27m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 3:47 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357323</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Sailandra Thapa</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Sailandra Thapa</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9862427803</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:47:22 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9862427803</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:09:30 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:47:22 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Dhunchapakha, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr"/>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L21-3</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>7h 37m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 3:50 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357539</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Adhikari</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Adhikari</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9849255086</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9849255086</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:17:09 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.750377</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Manamaiju Temple Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>saritasarita4123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L38-4</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.309795</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>5h 33m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 3:49 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357539</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Adhikari</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Adhikari</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9849255086</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9849255086</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:17:09 AM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.750377</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Manamaiju Temple Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>saritasarita4123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L38-4</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.309795</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>5h 33m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5608,7 +6424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5645,7 +6461,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -5655,7 +6471,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -5666,7 +6482,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -5678,7 +6494,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>29m</t>
+          <t>22m</t>
         </is>
       </c>
     </row>
@@ -5690,7 +6506,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 32m</t>
+          <t>17h 16m</t>
         </is>
       </c>
     </row>
@@ -5731,14 +6547,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
     </row>
@@ -5844,14 +6660,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -6941,14 +7757,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 09:21:42 AM</t>
@@ -6972,6 +7788,274 @@
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>6h 25m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357696</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Romiyana Neupane</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:17 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:22:10 AM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:49:17 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>4h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357323</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Sailandra Thapa</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:47:22 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:09:30 AM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:47:22 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>7h 37m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357539</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Sarita Adhikari</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:17:09 AM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>5h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357539</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Sarita Adhikari</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:17:09 AM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>5h 33m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="32" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -5656,10 +5656,8 @@
           <t>Romiyana Neupane</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9700393777</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9700393777</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -5749,10 +5747,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -5763,7 +5759,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -5859,10 +5855,8 @@
           <t>Sailandra Thapa</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9862427803</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9862427803</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -5948,10 +5942,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -5962,7 +5954,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6058,10 +6050,8 @@
           <t>Sarita Adhikari</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9849255086</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9849255086</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6096,10 +6086,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>27.750377</t>
-        </is>
+      <c r="Y31" s="3" t="n">
+        <v>27.750377</v>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
@@ -6155,25 +6143,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>L38-4</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.309795</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.30979499999999</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -6269,10 +6253,8 @@
           <t>Sarita Adhikari</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9849255086</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9849255086</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6307,10 +6289,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.750377</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.750377</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -6366,48 +6346,1489 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L38-4</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.309795</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.30979499999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>5h 33m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:02 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357283</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Khadgi Shrestha</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Khadgi Shrestha</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9803977028</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 07:38:15 AM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9803977028</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 07:38:15 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:02:29 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.710593</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Near New Arunodaya Secondary School Details from Google Maps Bijeshworu, P76X+9J2, Kathamndu  44600</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>khadgianisha64@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.300129</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>8h 24m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>8h 24m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:13 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi -6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi -6 router</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355547</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Jaisawal</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Kishan Jaisawal</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9813575302</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:13:00 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>CHB9813575302</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:52:51 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:13:00 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>new baneshwor, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>abc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Bhaskar Pant</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB622</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi -6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>5h 33m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi -6 router  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:11 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow isseu   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>slow isseu</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356892</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Samikshya Basnet Shrestha</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Samikshya Basnet Shrestha</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9744476666</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:11:25 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9818079691</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:21:07 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:11:25 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.69475</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Near INSEC Nepal, Near LRI school, Near Makalu Petrol pump, Kalanki, Kathmandu , Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>sujitshrestha070@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>02:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Keshab Magar</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.27792</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow isseu   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>22h 50m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW32" s="3" t="inlineStr">
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow isseu   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:08 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : dual band router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>dual band router</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357452</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Karki</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Karki</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9741840462</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:39:52 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9869618532</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:39:52 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:08:16 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.73214</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>near Radha Krishna Temple,tarkeshwor-16 balaju, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>karkisangita227@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.29913</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : dual band router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>6h 28m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>6h 28m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : dual band router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:07 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356549</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Ghimire</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Ghimire</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9841728801</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841728801</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:07:09 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>near by Peace Homestay - Homestay P7HV+QHM Janajagriti Marg Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>9841728801@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>06:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB352</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 23m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 23m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:06 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356549</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Ghimire</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Ghimire</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9841728801</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841728801</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:07:09 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>near by Peace Homestay - Homestay P7HV+QHM Janajagriti Marg Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>9841728801@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>06:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB352</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 23m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 23m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:05 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357158</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Bikram Kunwor</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Bikram Kunwor</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9843815726</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:33:15 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>KLK9843815726</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:33:15 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:05:52 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Global Vision School - High school P7HP+6MX 44608 Raniban Road Nagarjun 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>sujanbirkamkunwor10@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>CDB493</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6424,7 +7845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6461,7 +7882,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -6471,7 +7892,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -6482,7 +7903,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
     </row>
@@ -6494,7 +7915,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>22m</t>
+          <t>3h 52m</t>
         </is>
       </c>
     </row>
@@ -6506,7 +7927,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>17h 16m</t>
+          <t>17h 29m</t>
         </is>
       </c>
     </row>
@@ -6547,14 +7968,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -6577,74 +7998,69 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>General Query &amp; Feedback</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -6656,18 +8072,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6679,37 +8095,37 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>72.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -6725,7 +8141,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -6748,7 +8164,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -6764,238 +8180,150 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
       <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1355218</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Pramod Ojha</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 01:14:05 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:27:28 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 13m</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1356940</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Abhishek Kc</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 05:55:03 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>04 Oct 2026 10:58:58 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>17h 3m</t>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1357161</t>
+          <t>TKT1355218</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Pradip chandra Poudel</t>
+          <t>Pramod Ojha</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -7025,22 +8353,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 09:36:19 PM</t>
+          <t>02 Oct 2026 01:14:05 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:18:45 AM</t>
+          <t>04 Oct 2026 10:27:28 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -7050,19 +8378,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>13h 42m</t>
+          <t>1d 21h 13m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1355047</t>
+          <t>TKT1356940</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Unish Dulal</t>
+          <t>Abhishek Kc</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -7072,7 +8400,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -7092,22 +8420,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:44:04 AM</t>
+          <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 11:58:05 AM</t>
+          <t>03 Oct 2026 05:55:03 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:44:04 AM</t>
+          <t>04 Oct 2026 10:58:58 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -7117,29 +8445,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 45m</t>
+          <t>17h 3m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1356346</t>
+          <t>TKT1357161</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Suresh maharjan</t>
+          <t>Pradip chandra Poudel</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -7159,22 +8487,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:57:03 AM</t>
+          <t>04 Oct 2026 11:18:45 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:20:49 AM</t>
+          <t>03 Oct 2026 09:36:19 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:57:03 AM</t>
+          <t>04 Oct 2026 11:18:45 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -7184,19 +8512,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 36m</t>
+          <t>13h 42m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1356614</t>
+          <t>TKT1355047</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Surendra Aryal</t>
+          <t>Unish Dulal</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7206,7 +8534,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -7226,22 +8554,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:03:09 PM</t>
+          <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:18:47 PM</t>
+          <t>02 Oct 2026 11:58:05 AM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:03:09 PM</t>
+          <t>04 Oct 2026 11:44:04 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -7251,29 +8579,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>21h 44m</t>
+          <t>1d 23h 45m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1357724</t>
+          <t>TKT1356346</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Tara Natha Yogi</t>
+          <t>Suresh maharjan</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -7293,22 +8621,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : IPTV issue  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:23:38 PM</t>
+          <t>04 Oct 2026 11:57:03 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:39:55 AM</t>
+          <t>03 Oct 2026 11:20:49 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:23:38 PM</t>
+          <t>04 Oct 2026 11:57:03 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -7318,19 +8646,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>43m</t>
+          <t>1d 36m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1355876</t>
+          <t>TKT1356614</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Kamal Khatri</t>
+          <t>Surendra Aryal</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -7360,22 +8688,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:45:35 PM</t>
+          <t>04 Oct 2026 12:03:09 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 07:38:32 PM</t>
+          <t>03 Oct 2026 02:18:47 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:45:35 PM</t>
+          <t>04 Oct 2026 12:03:09 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -7385,29 +8713,29 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 17h 7m</t>
+          <t>21h 44m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1356999</t>
+          <t>TKT1357724</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Kapil Basnet</t>
+          <t>Tara Natha Yogi</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -7427,22 +8755,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:13 PM</t>
+          <t>04 Oct 2026 12:23:38 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 06:44:04 PM</t>
+          <t>04 Oct 2026 11:39:55 AM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:37:13 PM</t>
+          <t>04 Oct 2026 12:23:38 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -7452,19 +8780,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>17h 53m</t>
+          <t>43m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1357672</t>
+          <t>TKT1355876</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Dinesh Shrestha</t>
+          <t>Kamal Khatri</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7494,22 +8822,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:43:41 PM</t>
+          <t>04 Oct 2026 12:45:35 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:12:11 AM</t>
+          <t>02 Oct 2026 07:38:32 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:43:41 PM</t>
+          <t>04 Oct 2026 12:45:35 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -7519,39 +8847,39 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>1h 31m</t>
+          <t>1d 17h 7m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1357801</t>
+          <t>TKT1356999</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Dammar Bahadur Gurung</t>
+          <t>Kapil Basnet</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -7561,54 +8889,54 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:15:52 PM</t>
+          <t>04 Oct 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:15:52 PM</t>
+          <t>03 Oct 2026 06:44:04 PM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:40:37 PM</t>
+          <t>04 Oct 2026 12:37:13 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>24m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>24m</t>
+          <t>17h 53m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1357818</t>
+          <t>TKT1357672</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Uma Manandhar</t>
+          <t>Dinesh Shrestha</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -7628,22 +8956,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
+          <t>Case : upgrade wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:02:21 PM</t>
+          <t>04 Oct 2026 12:43:41 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 12:22:29 PM</t>
+          <t>04 Oct 2026 11:12:11 AM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:02:21 PM</t>
+          <t>04 Oct 2026 12:43:41 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -7653,19 +8981,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>1h 39m</t>
+          <t>1h 31m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1355431</t>
+          <t>TKT1357801</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Ramkhrishna Mijar</t>
+          <t>Dammar Bahadur Gurung</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -7680,12 +9008,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -7695,64 +9023,64 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6   has been updated by Sabin Giri</t>
+          <t>Case : upgrade wiif 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:18:12 PM</t>
+          <t>04 Oct 2026 12:15:52 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:33:53 PM</t>
+          <t>04 Oct 2026 12:15:52 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 02:18:12 PM</t>
+          <t>04 Oct 2026 12:40:37 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>24m</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 44m</t>
+          <t>24m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1357417</t>
+          <t>TKT1357818</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Swisha Adventure Travel</t>
+          <t>Uma Manandhar</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -7762,44 +9090,44 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>Case : IPTV not working  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 09:21:42 AM</t>
+          <t>04 Oct 2026 02:02:21 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 09:21:42 AM</t>
+          <t>04 Oct 2026 12:22:29 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 03:46:58 PM</t>
+          <t>04 Oct 2026 02:02:21 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>6h 25m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>6h 25m</t>
+          <t>1h 39m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1357696</t>
+          <t>TKT1355431</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Romiyana Neupane</t>
+          <t>Ramkhrishna Mijar</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7824,27 +9152,27 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 03:49:17 PM</t>
+          <t>04 Oct 2026 02:18:12 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 11:22:10 AM</t>
+          <t>02 Oct 2026 02:33:53 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 03:49:17 PM</t>
+          <t>04 Oct 2026 02:18:12 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -7854,19 +9182,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>4h 27m</t>
+          <t>1d 23h 44m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1357323</t>
+          <t>TKT1357417</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Sailandra Thapa</t>
+          <t>Swisha Adventure Travel</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -7881,59 +9209,59 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 03:47:22 PM</t>
+          <t>04 Oct 2026 09:21:42 AM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 08:09:30 AM</t>
+          <t>04 Oct 2026 09:21:42 AM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>04 Oct 2026 03:47:22 PM</t>
+          <t>04 Oct 2026 03:46:58 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>6h 25m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>7h 37m</t>
+          <t>6h 25m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1357539</t>
+          <t>TKT1357696</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Sarita Adhikari</t>
+          <t>Romiyana Neupane</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7958,27 +9286,27 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 03:50:51 PM</t>
+          <t>04 Oct 2026 03:49:17 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 10:17:09 AM</t>
+          <t>04 Oct 2026 11:22:10 AM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>04 Oct 2026 03:50:51 PM</t>
+          <t>04 Oct 2026 03:49:17 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -7988,74 +9316,610 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>5h 33m</t>
+          <t>4h 27m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>TKT1357323</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Sailandra Thapa</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:47:22 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 08:09:30 AM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:47:22 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>7h 37m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
           <t>TKT1357539</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Sarita Adhikari</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:17:09 AM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:50:51 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>5h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357539</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Sarita Adhikari</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 03:50:51 PM</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 10:17:09 AM</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 03:50:51 PM</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>5h 33m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357283</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Khadgi Shrestha</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 07:38:15 AM</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 07:38:15 AM</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:02:29 PM</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>8h 24m</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>8h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356892</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Samikshya Basnet Shrestha</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow isseu   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow isseu   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:11:25 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:21:07 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:11:25 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>22h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357452</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Karki</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : dual band router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : dual band router  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:39:52 AM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 09:39:52 AM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:08:16 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>6h 28m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>6h 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356549</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Ambika Ghimire</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:07:09 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 23m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356549</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Ghimire</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:44:08 PM</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:07:09 PM</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 23m</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 23m</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357158</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Sujan Bikram Kunwor</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:33:15 PM</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:33:15 PM</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:05:52 PM</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW39"/>
+  <dimension ref="A1:AW41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6456,10 +6456,8 @@
           <t>Asmita Khadgi Shrestha</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9803977028</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9803977028</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -6494,10 +6492,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.710593</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.710593</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -6553,25 +6549,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.300129</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.300129</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -6667,10 +6659,8 @@
           <t>Kishan Jaisawal</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9813575302</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9813575302</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -6756,10 +6746,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -6770,7 +6758,7 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi -6 router  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -6866,10 +6854,8 @@
           <t>Samikshya Basnet Shrestha</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9744476666</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9744476666</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -6904,10 +6890,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.69475</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.69475</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -6945,10 +6929,8 @@
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="AH35" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH35" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
@@ -6967,25 +6949,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.27792</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.27791999999999</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : slow isseu   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7081,10 +7059,8 @@
           <t>Saroj Karki</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9741840462</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9741840462</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7119,10 +7095,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.73214</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.73214</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7178,25 +7152,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.29913</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.29913000000001</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : dual band router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7292,10 +7262,8 @@
           <t>Ambika Ghimire</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9841728801</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9841728801</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7385,10 +7353,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -7399,7 +7365,7 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7495,10 +7461,8 @@
           <t>Ambika Ghimire</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9841728801</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9841728801</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7588,10 +7552,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -7602,7 +7564,7 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7698,10 +7660,8 @@
           <t>Sujan Bikram Kunwor</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9843815726</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9843815726</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7791,10 +7751,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -7805,32 +7763,430 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:28 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356661</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Raman Chaudhary</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Raman Chaudhary</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9705574992</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:31:44 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9815689195</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:53:34 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:28:05 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Samakhusi Children park, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>05:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>3,16</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>22h 56m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 34m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW39" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:27 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356661</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Raman Chaudhary</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Raman Chaudhary</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9705574992</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:31:44 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9815689195</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:53:34 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:28:05 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Samakhusi Children park, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>05:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>3,16</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr"/>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>22h 56m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 34m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -7845,7 +8201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7882,7 +8238,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -7892,7 +8248,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -7903,7 +8259,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -7915,7 +8271,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>3h 52m</t>
+          <t>5h 20m</t>
         </is>
       </c>
     </row>
@@ -7927,7 +8283,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>17h 29m</t>
+          <t>18h 6m</t>
         </is>
       </c>
     </row>
@@ -8004,10 +8360,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -8214,10 +8570,10 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -9554,7 +9910,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -9621,7 +9977,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : slow isseu   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -9688,7 +10044,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : dual band router  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -9755,7 +10111,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -9822,7 +10178,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -9889,14 +10245,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>03 Oct 2026 09:33:15 PM</t>
@@ -9920,6 +10276,140 @@
       <c r="M51" s="5" t="inlineStr">
         <is>
           <t>18h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356661</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Raman Chaudhary</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:31:44 PM</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:53:34 PM</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:28:05 PM</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>22h 56m</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 34m</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356661</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Raman Chaudhary</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 05:31:44 PM</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:53:34 PM</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:28:05 PM</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>22h 56m</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 34m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW41"/>
+  <dimension ref="A1:AW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -512,12 +512,12 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="19" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="32" customWidth="1" min="32" max="32"/>
+    <col width="33" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -7859,10 +7859,8 @@
           <t>Raman Chaudhary</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9705574992</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9705574992</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -7948,10 +7946,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
@@ -7962,7 +7958,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8058,10 +8054,8 @@
           <t>Raman Chaudhary</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9705574992</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9705574992</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8147,10 +8141,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
@@ -8161,30 +8153,241 @@
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>22h 56m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 34m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
           <t>Case : slow issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>22h 56m</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 34m</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV41" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:42 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351495</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Shaping Minds Group</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Shaping Minds Group</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9864477088</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:42:58 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9864477088S</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:15:57 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:42:58 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.70082</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Shaping Minds Group - Education for All (Pvt). Ltd. new plaza near Shaping Minds Group - Education f</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>accounts@shapingmindsgroup.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>21:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.3237</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>5d 2h 27m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -8201,7 +8404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8238,7 +8441,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -8248,7 +8451,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -8259,7 +8462,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8474,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 20m</t>
+          <t>5h 8m</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8486,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 6m</t>
+          <t>21h 58m</t>
         </is>
       </c>
     </row>
@@ -8324,14 +8527,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -8455,14 +8658,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
@@ -10312,7 +10515,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -10379,14 +10582,14 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
           <t>Case : slow issue   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Case : slow issue   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
           <t>03 Oct 2026 05:31:44 PM</t>
@@ -10410,6 +10613,73 @@
       <c r="M53" s="5" t="inlineStr">
         <is>
           <t>1d 1h 34m</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351495</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Shaping Minds Group</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:42:58 PM</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:15:57 PM</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:42:58 PM</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>5d 2h 27m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW42"/>
+  <dimension ref="A1:AW43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8249,10 +8249,8 @@
           <t>Shaping Minds Group</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9864477088</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9864477088</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8287,10 +8285,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.70082</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.70082</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -8346,48 +8342,255 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.3237</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.3237</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>5d 2h 27m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS42" s="3" t="inlineStr">
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 4:59 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356633</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Bisant Shakya</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Bisant Shakya</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9843101524</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:59:20 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9843101524</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:34:59 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:59:20 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.67558</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>pimbahal pokhari, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>bisant.shakya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>05:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.32143</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>5d 2h 27m</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 24m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV42" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW42" s="3" t="inlineStr">
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -8404,7 +8607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8441,7 +8644,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -8451,7 +8654,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -8462,7 +8665,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8677,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 8m</t>
+          <t>4h 57m</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8689,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 58m</t>
+          <t>22h 8m</t>
         </is>
       </c>
     </row>
@@ -8527,14 +8730,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -8658,14 +8861,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>74.1%</t>
         </is>
       </c>
     </row>
@@ -10649,14 +10852,14 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
           <t>04 Oct 2026 04:42:58 PM</t>
@@ -10680,6 +10883,73 @@
       <c r="M54" s="3" t="inlineStr">
         <is>
           <t>5d 2h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356633</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Bisant Shakya</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:59:20 PM</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:34:59 PM</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 04:59:20 PM</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 24m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW43"/>
+  <dimension ref="A1:AW44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -515,7 +515,7 @@
     <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="33" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
@@ -8452,10 +8452,8 @@
           <t>Bisant Shakya</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9843101524</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9843101524</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -8490,10 +8488,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.67558</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.67558</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -8549,48 +8545,255 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.32143</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.32143000000001</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 24m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 5:08 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : new router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>new router</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357534</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Anish Shrestha</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Anish Shrestha</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9860470589</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:08:43 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9860470589</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:15:53 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:08:43 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>27.7212</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>chuchhepati, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>icecake420@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr"/>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>85.35511</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : new router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 24m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>6h 52m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : new router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -8607,7 +8810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8644,7 +8847,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -8654,7 +8857,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -8665,7 +8868,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
     </row>
@@ -8677,7 +8880,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 57m</t>
+          <t>4h 47m</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8892,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 8m</t>
+          <t>21h 36m</t>
         </is>
       </c>
     </row>
@@ -8730,14 +8933,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>74.2%</t>
         </is>
       </c>
     </row>
@@ -8861,14 +9064,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -10919,14 +11122,14 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 04:59:20 PM</t>
@@ -10950,6 +11153,73 @@
       <c r="M55" s="5" t="inlineStr">
         <is>
           <t>1d 2h 24m</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357534</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Anish Shrestha</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Case : new router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : new router   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:08:43 PM</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 10:15:53 AM</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:08:43 PM</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>6h 52m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8655,10 +8655,8 @@
           <t>Anish Shrestha</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9860470589</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9860470589</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -8693,10 +8691,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>27.7212</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>27.7212</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -8752,25 +8748,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>4,8</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>85.35511</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>85.35511</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : new router   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -8819,7 +8811,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -11189,7 +11181,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Case : new router   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW44"/>
+  <dimension ref="A1:AW46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8791,6 +8791,412 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 6:00 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357681</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Shirish Tiwari</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Shirish Tiwari</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9841769071</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:00:32 PM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9841769071</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:15:17 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:00:32 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.67119</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Telecom - Telecommunications service provider M87Q+579 Imadol Marg Mahalaxmi 44700, Bagmati, N</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>tiwari.siris@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.32219</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>6h 45m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 5:52 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>no light in router</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357908</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman  Tharu</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Reopen</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman  Tharu</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9864350505</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:59:30 PM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9864350505</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 01:13:00 PM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 05:59:30 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Tikathali Khane pani Tikathali Khane pani - Drinking water fountain M944+4JW 44600, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>4h 46m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (Reopen)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light in router   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8802,7 +9208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8811,7 +9217,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -8839,7 +9245,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -8849,7 +9255,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -8860,7 +9266,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -8872,7 +9278,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 47m</t>
+          <t>4h 37m</t>
         </is>
       </c>
     </row>
@@ -8884,7 +9290,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 36m</t>
+          <t>21h 6m</t>
         </is>
       </c>
     </row>
@@ -8925,14 +9331,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -8943,14 +9349,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -9056,14 +9462,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -9148,14 +9554,14 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -11215,6 +11621,73 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357681</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Shirish Tiwari</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:00:32 PM</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:15:17 AM</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:00:32 PM</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
+          <t>6h 45m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW46"/>
+  <dimension ref="A1:AW50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8858,10 +8858,8 @@
           <t>Shirish Tiwari</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9841769071</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9841769071</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -8896,10 +8894,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.67119</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.67119</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -8955,25 +8951,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.32219</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.32219000000001</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -9069,10 +9061,8 @@
           <t>Laxman  Tharu</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9864350505</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9864350505</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -9154,10 +9144,8 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
@@ -9168,32 +9156,872 @@
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>4h 46m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (Reopen)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
           <t>Case : no light in router   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS46" s="3" t="inlineStr">
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 6:03 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357699</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9848875530</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:03:37 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9848875530</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:24:27 AM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:03:37 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.68251</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Lokanthali, Madhyapur Thimi, Next To Urbana Montessori School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>surajss40216@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>L7-7</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.3636</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>4h 46m</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (Reopen)</t>
-        </is>
-      </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light in router   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW46" s="3" t="inlineStr">
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>6h 39m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 6:02 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356482</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Ishwor Bodel</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Ishwor Bodel</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9841962855</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:01:58 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9841962855</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:05:05 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:01:58 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.664142</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>balkot near, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>06:55 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>L26-8</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.363679</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 56m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 6:15 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357172</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Acharya</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Acharya</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9867815013</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:59:51 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9867815013B</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:59:51 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:15:16 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.656161</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Taudaha,panchawati marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>prabikacharya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.27521</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 6:14 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357172</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Acharya</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Acharya</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9867815013</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:59:51 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9867815013B</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:59:51 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:15:16 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.656161</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Taudaha,panchawati marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>prabikacharya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.27521</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -9208,7 +10036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -9245,7 +10073,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -9255,7 +10083,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -9266,7 +10094,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.4%</t>
         </is>
       </c>
     </row>
@@ -9278,7 +10106,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 37m</t>
+          <t>5h 16m</t>
         </is>
       </c>
     </row>
@@ -9290,7 +10118,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 6m</t>
+          <t>20h 52m</t>
         </is>
       </c>
     </row>
@@ -9331,14 +10159,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -9462,14 +10290,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>78.8%</t>
         </is>
       </c>
     </row>
@@ -11654,14 +12482,14 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>04 Oct 2026 06:00:32 PM</t>
@@ -11685,6 +12513,274 @@
       <c r="M57" s="5" t="inlineStr">
         <is>
           <t>6h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357699</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Kumar Shrestha</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:03:37 PM</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 11:24:27 AM</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:03:37 PM</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>6h 39m</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356482</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Ishwor Bodel</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:01:58 PM</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:05:05 PM</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:01:58 PM</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>1d 4h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1357172</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Bibek Acharya</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:59:51 PM</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:59:51 PM</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:15:16 PM</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>TKT1357172</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Bibek Acharya</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:59:51 PM</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:59:51 PM</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:15:16 PM</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW50"/>
+  <dimension ref="A1:AW52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="33" customWidth="1" min="32" max="32"/>
+    <col width="34" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -9252,10 +9252,8 @@
           <t>Mohan Kumar Shrestha</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9848875530</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9848875530</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -9290,10 +9288,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.68251</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.68251</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -9349,25 +9345,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>L7-7</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.3636</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.36360000000001</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -9463,10 +9455,8 @@
           <t>Ishwor Bodel</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9841962855</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9841962855</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -9501,10 +9491,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.664142</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.664142</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -9556,25 +9544,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>L26-8</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.363679</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.363679</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -9670,10 +9654,8 @@
           <t>Bibek Acharya</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9867815013</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9867815013</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9708,10 +9690,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.656161</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.656161</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -9767,25 +9747,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.27521</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.27521</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -9881,10 +9857,8 @@
           <t>Bibek Acharya</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9867815013</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9867815013</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -9919,10 +9893,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.656161</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.656161</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -9978,48 +9950,458 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.27521</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.27521</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>20h 15m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS50" s="3" t="inlineStr">
-        <is>
-          <t>20h 15m</t>
-        </is>
-      </c>
-      <c r="AT50" s="3" t="inlineStr">
-        <is>
-          <t>20h 15m</t>
-        </is>
-      </c>
-      <c r="AU50" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV50" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 6:17 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358137</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Top Bahadur Adhikari</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Top Bahadur Adhikari</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9861644070</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:17:36 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>KLK9851062126</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:03:52 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:17:36 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Nepal CRS Company P8RC+QP4, Mahadevvtar, Tokha Road, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L25-7</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>3h 13m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 6:30 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : UPGRADE WIFI   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>UPGRADE WIFI</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358135</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Tamrakar</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Tamrakar</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9860915599</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:30:27 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9860915599</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:02:15 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:30:27 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.67113</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur Ibahal nyakhunaa shop, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>customercare@chaudharygroup.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>00:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.32387</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : UPGRADE WIFI   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>3h 28m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : UPGRADE WIFI   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -10036,7 +10418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -10073,7 +10455,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -10083,7 +10465,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -10094,7 +10476,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10488,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 16m</t>
+          <t>4h 59m</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10500,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 52m</t>
+          <t>19h 53m</t>
         </is>
       </c>
     </row>
@@ -10159,14 +10541,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.9%</t>
         </is>
       </c>
     </row>
@@ -10290,14 +10672,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -12549,7 +12931,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
@@ -12616,7 +12998,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -12683,7 +13065,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -12750,14 +13132,14 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>03 Oct 2026 09:59:51 PM</t>
@@ -12781,6 +13163,140 @@
       <c r="M61" s="5" t="inlineStr">
         <is>
           <t>20h 15m</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1358137</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Top Bahadur Adhikari</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:17:36 PM</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:03:52 PM</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:17:36 PM</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>3h 13m</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>TKT1358135</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Prajwal Tamrakar</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Case : UPGRADE WIFI   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Case : UPGRADE WIFI   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:30:27 PM</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 03:02:15 PM</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>04 Oct 2026 06:30:27 PM</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>3h 28m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_04_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_04_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10060,10 +10060,8 @@
           <t>Top Bahadur Adhikari</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9861644070</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9861644070</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10153,10 +10151,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10167,7 +10163,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10263,10 +10259,8 @@
           <t>Prajwal Tamrakar</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9860915599</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9860915599</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10301,10 +10295,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.67113</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.67113</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10360,25 +10352,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.32387</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.32387</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>Case : UPGRADE WIFI   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
@@ -10427,7 +10415,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -13199,7 +13187,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -13266,7 +13254,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Case : UPGRADE WIFI   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
